--- a/sheets/대금율보/검수/귀소.xlsx
+++ b/sheets/대금율보/검수/귀소.xlsx
@@ -3561,32 +3561,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="80.0" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="89.42" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="89.42" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="U4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="89.42" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
@@ -3765,7 +3765,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="89.42" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="24"/>
@@ -3817,7 +3817,7 @@
       <c r="T6" s="21"/>
       <c r="U6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="89.42" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
       <c r="T7" s="21"/>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="89.42" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="89.42" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -3942,7 +3942,7 @@
       <c r="T9" s="21"/>
       <c r="U9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="89.42" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="U10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="89.42" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="89.42" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="U12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="89.42" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -4153,7 +4153,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="89.42" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -4195,7 +4195,7 @@
       <c r="T14" s="21"/>
       <c r="U14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="89.42" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -4237,7 +4237,7 @@
       <c r="T15" s="21"/>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="89.42" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -4260,7 +4260,7 @@
       <c r="T16" s="21"/>
       <c r="U16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="89.42" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -4283,7 +4283,7 @@
       <c r="T17" s="21"/>
       <c r="U17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="89.42" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -4355,6 +4355,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
 </worksheet>
 </file>